--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git\autobot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_20DEDC917A87CC5A8D4669D459FC37227A99A8A9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C0583FC5B99F27E38B9C951D078237016E99B118" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4762" uniqueCount="3187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4795" uniqueCount="3209">
   <si>
     <t>Kỳ Quay</t>
   </si>
@@ -9523,10 +9523,76 @@
     <t>07/08/2026</t>
   </si>
   <si>
-    <t>15/08/2026</t>
-  </si>
-  <si>
-    <t>Thứ 7</t>
+    <t>#01575</t>
+  </si>
+  <si>
+    <t>09/08/2026</t>
+  </si>
+  <si>
+    <t>#01576</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>#01577</t>
+  </si>
+  <si>
+    <t>14/08/2026</t>
+  </si>
+  <si>
+    <t>#01578</t>
+  </si>
+  <si>
+    <t>16/08/2026</t>
+  </si>
+  <si>
+    <t>#01579</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>#01580</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t>#01581</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>#01582</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t>#01583</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>#01584</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>#01585</t>
+  </si>
+  <si>
+    <t>02/09/2026</t>
+  </si>
+  <si>
+    <t>#01586</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
   </si>
   <si>
     <t>HỆ THỐNG TRA CỨU &amp; THỐNG KÊ KẾT QUẢ VIETLOTT MEGA 6/45</t>
@@ -9607,7 +9673,7 @@
     <numFmt numFmtId="165" formatCode="#,##0\ &quot;lần&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;VNĐ&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9690,14 +9756,8 @@
       <color rgb="FF1E3A8A"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFB45309"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9738,12 +9798,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE0F2FE"/>
         <bgColor rgb="FFE0F2FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF3C7"/>
-        <bgColor rgb="FFFEF3C7"/>
       </patternFill>
     </fill>
   </fills>
@@ -9789,7 +9843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9842,9 +9896,6 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10223,7 +10274,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7568-46AA-8913-DA1E4510E457}"/>
+              <c16:uniqueId val="{00000000-83A6-49F5-BEEC-A6273BF3A356}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10656,72 +10707,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="23" t="s">
-        <v>3164</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
+      <c r="A1" s="22" t="s">
+        <v>3186</v>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>3165</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
+      <c r="A2" s="26" t="s">
+        <v>3187</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>3166</v>
-      </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="20" t="s">
-        <v>3167</v>
-      </c>
-      <c r="D4" s="21"/>
-      <c r="E4" s="20" t="s">
-        <v>3168</v>
-      </c>
-      <c r="F4" s="21"/>
+      <c r="A4" s="19" t="s">
+        <v>3188</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="19" t="s">
+        <v>3189</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="19" t="s">
+        <v>3190</v>
+      </c>
+      <c r="F4" s="20"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+      <c r="A5" s="24">
         <f>COUNTA('Lịch Sử Số Trúng (1200+ Kỳ)'!A2:A1575)</f>
         <v>1574</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="25">
+      <c r="B5" s="20"/>
+      <c r="C5" s="24">
         <f>MAX('Lịch Sử Số Trúng (1200+ Kỳ)'!J2:J1575)</f>
         <v>313665163989</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="25">
+      <c r="D5" s="20"/>
+      <c r="E5" s="24">
         <f>SUM('Lịch Sử Số Trúng (1200+ Kỳ)'!K2:K1575)</f>
         <v>33</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="20"/>
     </row>
     <row r="7" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="26" t="s">
-        <v>3169</v>
-      </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
+      <c r="A7" s="25" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
     </row>
     <row r="8" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>3170</v>
+        <v>3192</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
@@ -10729,84 +10780,84 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>3171</v>
-      </c>
-      <c r="C10" s="22" t="str">
+        <v>3193</v>
+      </c>
+      <c r="C10" s="21" t="str">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 2, FALSE), "Không tìm thấy")</f>
         <v>20/07/2016</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>3172</v>
-      </c>
-      <c r="C11" s="22" t="str">
+        <v>3194</v>
+      </c>
+      <c r="C11" s="21" t="str">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 3, FALSE), "-")</f>
         <v>Thứ 4</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
     </row>
     <row r="12" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>3173</v>
-      </c>
-      <c r="C12" s="28" t="str">
+        <v>3195</v>
+      </c>
+      <c r="C12" s="27" t="str">
         <f ca="1">IFERROR(_xludf.TEXTJOIN("  -  ", TRUE, TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 4, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 5, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 6, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 7, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 8, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 9, FALSE), "00")), "-")</f>
         <v>-</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>3174</v>
-      </c>
-      <c r="C13" s="24">
+        <v>3196</v>
+      </c>
+      <c r="C13" s="23">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 10, FALSE), "-")</f>
         <v>12000000000</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>3175</v>
-      </c>
-      <c r="C14" s="22">
+        <v>3197</v>
+      </c>
+      <c r="C14" s="21">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 11, FALSE), "-")</f>
         <v>0</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
     </row>
     <row r="16" spans="1:7" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="26" t="s">
-        <v>3176</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+      <c r="A16" s="25" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>3177</v>
+        <v>3199</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>3178</v>
+        <v>3200</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>3179</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>3180</v>
+        <v>3202</v>
       </c>
       <c r="B18" s="5">
         <f>INDEX('Thống Kê Tần Suất'!A$2:A$46, MATCH(LARGE('Thống Kê Tần Suất'!B$2:B$46, 1), 'Thống Kê Tần Suất'!B$2:B$46, 0))</f>
@@ -10819,7 +10870,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>3181</v>
+        <v>3203</v>
       </c>
       <c r="B19" s="5">
         <f>INDEX('Thống Kê Tần Suất'!A$2:A$46, MATCH(LARGE('Thống Kê Tần Suất'!B$2:B$46, 2), 'Thống Kê Tần Suất'!B$2:B$46, 0))</f>
@@ -10832,7 +10883,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>3182</v>
+        <v>3204</v>
       </c>
       <c r="B20" s="5">
         <f>INDEX('Thống Kê Tần Suất'!A$2:A$46, MATCH(LARGE('Thống Kê Tần Suất'!B$2:B$46, 3), 'Thống Kê Tần Suất'!B$2:B$46, 0))</f>
@@ -10845,7 +10896,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>3183</v>
+        <v>3205</v>
       </c>
       <c r="B21" s="5">
         <f>INDEX('Thống Kê Tần Suất'!A$2:A$46, MATCH(LARGE('Thống Kê Tần Suất'!B$2:B$46, 4), 'Thống Kê Tần Suất'!B$2:B$46, 0))</f>
@@ -10858,7 +10909,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>3184</v>
+        <v>3206</v>
       </c>
       <c r="B22" s="5">
         <f>INDEX('Thống Kê Tần Suất'!A$2:A$46, MATCH(LARGE('Thống Kê Tần Suất'!B$2:B$46, 5), 'Thống Kê Tần Suất'!B$2:B$46, 0))</f>
@@ -10879,8 +10930,8 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -10893,7 +10944,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K1576"/>
+  <dimension ref="A1:K1587"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -66030,37 +66081,422 @@
     </row>
     <row r="1576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1576" s="16" t="s">
-        <v>926</v>
+        <v>3162</v>
       </c>
       <c r="B1576" s="16" t="s">
-        <v>3162</v>
+        <v>3163</v>
       </c>
       <c r="C1576" s="16" t="s">
-        <v>3163</v>
+        <v>19</v>
       </c>
       <c r="D1576" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1576" s="17">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F1576" s="17">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="G1576" s="17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H1576" s="17">
         <v>31</v>
       </c>
       <c r="I1576" s="17">
+        <v>35</v>
+      </c>
+      <c r="J1576" s="18">
+        <v>16447584000</v>
+      </c>
+      <c r="K1576" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1577" s="16" t="s">
+        <v>3164</v>
+      </c>
+      <c r="B1577" s="16" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1577" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1577" s="17">
+        <v>15</v>
+      </c>
+      <c r="E1577" s="17">
+        <v>17</v>
+      </c>
+      <c r="F1577" s="17">
+        <v>22</v>
+      </c>
+      <c r="G1577" s="17">
+        <v>29</v>
+      </c>
+      <c r="H1577" s="17">
+        <v>33</v>
+      </c>
+      <c r="I1577" s="17">
+        <v>40</v>
+      </c>
+      <c r="J1577" s="18">
+        <v>18210978000</v>
+      </c>
+      <c r="K1577" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1578" s="16" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B1578" s="16" t="s">
+        <v>3167</v>
+      </c>
+      <c r="C1578" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1578" s="17">
+        <v>7</v>
+      </c>
+      <c r="E1578" s="17">
+        <v>9</v>
+      </c>
+      <c r="F1578" s="17">
+        <v>13</v>
+      </c>
+      <c r="G1578" s="17">
+        <v>31</v>
+      </c>
+      <c r="H1578" s="17">
+        <v>35</v>
+      </c>
+      <c r="I1578" s="17">
+        <v>44</v>
+      </c>
+      <c r="J1578" s="18">
+        <v>20050493000</v>
+      </c>
+      <c r="K1578" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1579" s="16" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B1579" s="16" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1579" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1579" s="17">
+        <v>6</v>
+      </c>
+      <c r="E1579" s="17">
+        <v>7</v>
+      </c>
+      <c r="F1579" s="17">
+        <v>15</v>
+      </c>
+      <c r="G1579" s="17">
+        <v>19</v>
+      </c>
+      <c r="H1579" s="17">
+        <v>36</v>
+      </c>
+      <c r="I1579" s="17">
+        <v>41</v>
+      </c>
+      <c r="J1579" s="18">
+        <v>22133497500</v>
+      </c>
+      <c r="K1579" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1580" s="16" t="s">
+        <v>3170</v>
+      </c>
+      <c r="B1580" s="16" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C1580" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1580" s="17">
+        <v>6</v>
+      </c>
+      <c r="E1580" s="17">
+        <v>15</v>
+      </c>
+      <c r="F1580" s="17">
+        <v>18</v>
+      </c>
+      <c r="G1580" s="17">
+        <v>33</v>
+      </c>
+      <c r="H1580" s="17">
+        <v>40</v>
+      </c>
+      <c r="I1580" s="17">
+        <v>43</v>
+      </c>
+      <c r="J1580" s="18">
+        <v>24507110500</v>
+      </c>
+      <c r="K1580" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1581" s="16" t="s">
+        <v>3172</v>
+      </c>
+      <c r="B1581" s="16" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C1581" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1581" s="17">
+        <v>7</v>
+      </c>
+      <c r="E1581" s="17">
+        <v>26</v>
+      </c>
+      <c r="F1581" s="17">
+        <v>31</v>
+      </c>
+      <c r="G1581" s="17">
+        <v>38</v>
+      </c>
+      <c r="H1581" s="17">
+        <v>43</v>
+      </c>
+      <c r="I1581" s="17">
+        <v>45</v>
+      </c>
+      <c r="J1581" s="18">
+        <v>26637873000</v>
+      </c>
+      <c r="K1581" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1582" s="16" t="s">
+        <v>3174</v>
+      </c>
+      <c r="B1582" s="16" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1582" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1582" s="17">
+        <v>4</v>
+      </c>
+      <c r="E1582" s="17">
+        <v>16</v>
+      </c>
+      <c r="F1582" s="17">
+        <v>17</v>
+      </c>
+      <c r="G1582" s="17">
+        <v>22</v>
+      </c>
+      <c r="H1582" s="17">
+        <v>32</v>
+      </c>
+      <c r="I1582" s="17">
         <v>39</v>
       </c>
-      <c r="J1576" s="18">
-        <v>50000000</v>
-      </c>
-      <c r="K1576" s="19">
+      <c r="J1582" s="18">
+        <v>28975123500</v>
+      </c>
+      <c r="K1582" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1583" s="16" t="s">
+        <v>3176</v>
+      </c>
+      <c r="B1583" s="16" t="s">
+        <v>3177</v>
+      </c>
+      <c r="C1583" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1583" s="17">
+        <v>3</v>
+      </c>
+      <c r="E1583" s="17">
+        <v>10</v>
+      </c>
+      <c r="F1583" s="17">
+        <v>11</v>
+      </c>
+      <c r="G1583" s="17">
+        <v>16</v>
+      </c>
+      <c r="H1583" s="17">
+        <v>33</v>
+      </c>
+      <c r="I1583" s="17">
+        <v>40</v>
+      </c>
+      <c r="J1583" s="18">
+        <v>31682191000</v>
+      </c>
+      <c r="K1583" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1584" s="16" t="s">
+        <v>3178</v>
+      </c>
+      <c r="B1584" s="16" t="s">
+        <v>3179</v>
+      </c>
+      <c r="C1584" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1584" s="17">
+        <v>3</v>
+      </c>
+      <c r="E1584" s="17">
+        <v>13</v>
+      </c>
+      <c r="F1584" s="17">
+        <v>15</v>
+      </c>
+      <c r="G1584" s="17">
+        <v>22</v>
+      </c>
+      <c r="H1584" s="17">
+        <v>36</v>
+      </c>
+      <c r="I1584" s="17">
+        <v>39</v>
+      </c>
+      <c r="J1584" s="18">
+        <v>33904731500</v>
+      </c>
+      <c r="K1584" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1585" s="16" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B1585" s="16" t="s">
+        <v>3181</v>
+      </c>
+      <c r="C1585" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1585" s="17">
         <v>1</v>
+      </c>
+      <c r="E1585" s="17">
+        <v>3</v>
+      </c>
+      <c r="F1585" s="17">
+        <v>12</v>
+      </c>
+      <c r="G1585" s="17">
+        <v>15</v>
+      </c>
+      <c r="H1585" s="17">
+        <v>37</v>
+      </c>
+      <c r="I1585" s="17">
+        <v>45</v>
+      </c>
+      <c r="J1585" s="18">
+        <v>36644788500</v>
+      </c>
+      <c r="K1585" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1586" s="16" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B1586" s="16" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C1586" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1586" s="17">
+        <v>6</v>
+      </c>
+      <c r="E1586" s="17">
+        <v>9</v>
+      </c>
+      <c r="F1586" s="17">
+        <v>27</v>
+      </c>
+      <c r="G1586" s="17">
+        <v>29</v>
+      </c>
+      <c r="H1586" s="17">
+        <v>35</v>
+      </c>
+      <c r="I1586" s="17">
+        <v>44</v>
+      </c>
+      <c r="J1586" s="18">
+        <v>38804848000</v>
+      </c>
+      <c r="K1586" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1587" s="16" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B1587" s="16" t="s">
+        <v>3185</v>
+      </c>
+      <c r="C1587" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1587" s="17">
+        <v>16</v>
+      </c>
+      <c r="E1587" s="17">
+        <v>21</v>
+      </c>
+      <c r="F1587" s="17">
+        <v>23</v>
+      </c>
+      <c r="G1587" s="17">
+        <v>29</v>
+      </c>
+      <c r="H1587" s="17">
+        <v>34</v>
+      </c>
+      <c r="I1587" s="17">
+        <v>45</v>
+      </c>
+      <c r="J1587" s="18">
+        <v>43022978000</v>
+      </c>
+      <c r="K1587" s="16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -66081,16 +66517,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>3178</v>
+        <v>3200</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>3179</v>
+        <v>3201</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>3185</v>
+        <v>3207</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>3186</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -1315,9 +1315,9 @@
   <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C11:E11"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C14:E14"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
@@ -65497,34 +65497,34 @@
       </c>
       <c r="B1565" s="8" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>18/09/2026</t>
         </is>
       </c>
       <c r="C1565" s="8" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1565" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1565" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F1565" s="9" t="n">
         <v>26</v>
       </c>
       <c r="G1565" s="9" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H1565" s="9" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I1565" s="9" t="n">
         <v>43</v>
       </c>
       <c r="J1565" s="10" t="n">
-        <v>101885579123</v>
+        <v>86148921500</v>
       </c>
       <c r="K1565" s="8" t="n">
         <v>0</v>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Tổng Quan &amp; Tra Cứu" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lịch Sử Số Trúng (1200+ Kỳ)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Thống Kê Tần Suất" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tổng Quan &amp; Tra Cứu" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lịch Sử Số Trúng (1200+ Kỳ)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thống Kê Tần Suất" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -246,17 +246,12 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -264,6 +259,11 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -342,14 +342,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -382,7 +382,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -544,7 +544,7 @@
                   <v>177</v>
                 </pt>
                 <pt idx="2">
-                  <v>205</v>
+                  <v>203</v>
                 </pt>
                 <pt idx="3">
                   <v>201</v>
@@ -553,25 +553,25 @@
                   <v>214</v>
                 </pt>
                 <pt idx="5">
-                  <v>237</v>
+                  <v>238</v>
                 </pt>
                 <pt idx="6">
-                  <v>222</v>
+                  <v>223</v>
                 </pt>
                 <pt idx="7">
                   <v>222</v>
                 </pt>
                 <pt idx="8">
-                  <v>221</v>
+                  <v>220</v>
                 </pt>
                 <pt idx="9">
                   <v>228</v>
                 </pt>
                 <pt idx="10">
-                  <v>217</v>
+                  <v>218</v>
                 </pt>
                 <pt idx="11">
-                  <v>206</v>
+                  <v>207</v>
                 </pt>
                 <pt idx="12">
                   <v>203</v>
@@ -610,19 +610,19 @@
                   <v>214</v>
                 </pt>
                 <pt idx="24">
-                  <v>207</v>
+                  <v>208</v>
                 </pt>
                 <pt idx="25">
                   <v>204</v>
                 </pt>
                 <pt idx="26">
-                  <v>214</v>
+                  <v>216</v>
                 </pt>
                 <pt idx="27">
                   <v>217</v>
                 </pt>
                 <pt idx="28">
-                  <v>221</v>
+                  <v>220</v>
                 </pt>
                 <pt idx="29">
                   <v>210</v>
@@ -637,40 +637,40 @@
                   <v>194</v>
                 </pt>
                 <pt idx="33">
-                  <v>209</v>
+                  <v>207</v>
                 </pt>
                 <pt idx="34">
-                  <v>209</v>
+                  <v>208</v>
                 </pt>
                 <pt idx="35">
                   <v>198</v>
                 </pt>
                 <pt idx="36">
-                  <v>216</v>
+                  <v>217</v>
                 </pt>
                 <pt idx="37">
                   <v>192</v>
                 </pt>
                 <pt idx="38">
-                  <v>228</v>
+                  <v>227</v>
                 </pt>
                 <pt idx="39">
                   <v>191</v>
                 </pt>
                 <pt idx="40">
-                  <v>216</v>
+                  <v>217</v>
                 </pt>
                 <pt idx="41">
                   <v>219</v>
                 </pt>
                 <pt idx="42">
-                  <v>213</v>
+                  <v>212</v>
                 </pt>
                 <pt idx="43">
-                  <v>249</v>
+                  <v>248</v>
                 </pt>
                 <pt idx="44">
-                  <v>205</v>
+                  <v>206</v>
                 </pt>
               </numCache>
             </numRef>
@@ -698,9 +698,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -734,9 +734,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -768,7 +768,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>4</col>
@@ -783,9 +783,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1084,7 +1084,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="28" customWidth="1" style="20" min="1" max="1"/>
     <col width="18" customWidth="1" style="20" min="2" max="2"/>
@@ -1093,53 +1093,53 @@
     <col width="12" customWidth="1" style="20" min="6" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="23.45" customHeight="1" s="20">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="23.4" customHeight="1" s="20">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>HỆ THỐNG TRA CỨU &amp; THỐNG KÊ KẾT QUẢ VIETLOTT MEGA 6/45</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Dữ liệu tổng hợp từ Kỳ 00001 (18/07/2016) đến Kỳ #01574 (07/08/2026)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>Tổng Số Kỳ Quay</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Jackpot Cao Nhất</t>
         </is>
       </c>
-      <c r="E4" s="24" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Tổng Số Vé Trúng JP</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="20">
-      <c r="A5" s="27">
+      <c r="A5" s="24">
         <f>COUNTA('Lịch Sử Số Trúng (1200+ Kỳ)'!A2:A1575)</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="24">
         <f>MAX('Lịch Sử Số Trúng (1200+ Kỳ)'!J2:J1575)</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="24">
         <f>SUM('Lịch Sử Số Trúng (1200+ Kỳ)'!K2:K1575)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="17.45" customHeight="1" s="20">
-      <c r="A7" s="19" t="inlineStr">
+    <row r="7" ht="17.4" customHeight="1" s="20">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>🔍 TRA CỨU KẾT QUẢ TỰ ĐỘNG THEO KỲ QUAY</t>
         </is>
@@ -1163,7 +1163,7 @@
           <t>Ngày Mở Thưởng</t>
         </is>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="21">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 2, FALSE), "Không tìm thấy")</f>
         <v/>
       </c>
@@ -1174,7 +1174,7 @@
           <t>Thứ trong tuần</t>
         </is>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="21">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 3, FALSE), "-")</f>
         <v/>
       </c>
@@ -1185,7 +1185,7 @@
           <t>Bộ Số Trúng Thưởng</t>
         </is>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="27">
         <f>IFERROR(_xludf.TEXTJOIN("  -  ", TRUE, TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 4, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 5, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 6, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 7, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 8, FALSE), "00"), TEXT(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 9, FALSE), "00")), "-")</f>
         <v/>
       </c>
@@ -1196,7 +1196,7 @@
           <t>Giá Trị Jackpot</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="23">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 10, FALSE), "-")</f>
         <v/>
       </c>
@@ -1207,13 +1207,13 @@
           <t>Số Vé Trúng Jackpot</t>
         </is>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="21">
         <f>IFERROR(VLOOKUP(C8, 'Lịch Sử Số Trúng (1200+ Kỳ)'!A:K, 11, FALSE), "-")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="17.45" customHeight="1" s="20">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="16" ht="17.4" customHeight="1" s="20">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>🔥 TOP 5 CON SỐ XUẤT HIỆN NHIỀU NHẤT</t>
         </is>
@@ -1315,19 +1315,19 @@
   <mergeCells count="15">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="C13:E13"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C4:D4"/>
     <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1340,7 +1340,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K1587"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
     <col width="14" customWidth="1" style="20" min="2" max="2"/>
@@ -65492,12 +65492,12 @@
     <row r="1565">
       <c r="A1565" s="8" t="inlineStr">
         <is>
-          <t>#01564</t>
+          <t>#01565</t>
         </is>
       </c>
       <c r="B1565" s="8" t="inlineStr">
         <is>
-          <t>18/09/2026</t>
+          <t>17/07/2026</t>
         </is>
       </c>
       <c r="C1565" s="8" t="inlineStr">
@@ -65506,25 +65506,25 @@
         </is>
       </c>
       <c r="D1565" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1565" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E1565" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="F1565" s="9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G1565" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H1565" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="H1565" s="9" t="n">
-        <v>41</v>
-      </c>
       <c r="I1565" s="9" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="J1565" s="10" t="n">
-        <v>86148921500</v>
+        <v>102920523614</v>
       </c>
       <c r="K1565" s="8" t="n">
         <v>0</v>
@@ -65533,39 +65533,39 @@
     <row r="1566">
       <c r="A1566" s="8" t="inlineStr">
         <is>
-          <t>#01565</t>
+          <t>#01566</t>
         </is>
       </c>
       <c r="B1566" s="8" t="inlineStr">
         <is>
-          <t>17/07/2026</t>
+          <t>19/07/2026</t>
         </is>
       </c>
       <c r="C1566" s="8" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1566" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1566" s="9" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F1566" s="9" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G1566" s="9" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H1566" s="9" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="I1566" s="9" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="J1566" s="10" t="n">
-        <v>102920523614</v>
+        <v>104663176007</v>
       </c>
       <c r="K1566" s="8" t="n">
         <v>0</v>
@@ -65574,39 +65574,39 @@
     <row r="1567">
       <c r="A1567" s="8" t="inlineStr">
         <is>
-          <t>#01566</t>
+          <t>#01567</t>
         </is>
       </c>
       <c r="B1567" s="8" t="inlineStr">
         <is>
-          <t>19/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="C1567" s="8" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1567" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1567" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F1567" s="9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1567" s="9" t="n">
         <v>32</v>
       </c>
       <c r="H1567" s="9" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I1567" s="9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1567" s="10" t="n">
-        <v>104663176007</v>
+        <v>106304079214</v>
       </c>
       <c r="K1567" s="8" t="n">
         <v>0</v>
@@ -65615,39 +65615,39 @@
     <row r="1568">
       <c r="A1568" s="8" t="inlineStr">
         <is>
-          <t>#01567</t>
+          <t>#01568</t>
         </is>
       </c>
       <c r="B1568" s="8" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="C1568" s="8" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1568" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1568" s="9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F1568" s="9" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G1568" s="9" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H1568" s="9" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="I1568" s="9" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="J1568" s="10" t="n">
-        <v>106304079214</v>
+        <v>107524719451</v>
       </c>
       <c r="K1568" s="8" t="n">
         <v>0</v>
@@ -65656,39 +65656,39 @@
     <row r="1569">
       <c r="A1569" s="8" t="inlineStr">
         <is>
-          <t>#01568</t>
+          <t>#01569</t>
         </is>
       </c>
       <c r="B1569" s="8" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>26/07/2026</t>
         </is>
       </c>
       <c r="C1569" s="8" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1569" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1569" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F1569" s="9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="G1569" s="9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H1569" s="9" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I1569" s="9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J1569" s="10" t="n">
-        <v>107524719451</v>
+        <v>110374537746</v>
       </c>
       <c r="K1569" s="8" t="n">
         <v>0</v>
@@ -65697,39 +65697,39 @@
     <row r="1570">
       <c r="A1570" s="8" t="inlineStr">
         <is>
-          <t>#01569</t>
+          <t>#01570</t>
         </is>
       </c>
       <c r="B1570" s="8" t="inlineStr">
         <is>
-          <t>26/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="C1570" s="8" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1570" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E1570" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F1570" s="9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G1570" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H1570" s="9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I1570" s="9" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="J1570" s="10" t="n">
-        <v>110374537746</v>
+        <v>113118900044</v>
       </c>
       <c r="K1570" s="8" t="n">
         <v>0</v>
@@ -65738,39 +65738,39 @@
     <row r="1571">
       <c r="A1571" s="8" t="inlineStr">
         <is>
-          <t>#01570</t>
+          <t>#01571</t>
         </is>
       </c>
       <c r="B1571" s="8" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="C1571" s="8" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1571" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E1571" s="9" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F1571" s="9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G1571" s="9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H1571" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I1571" s="9" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J1571" s="10" t="n">
-        <v>113118900044</v>
+        <v>114772358051</v>
       </c>
       <c r="K1571" s="8" t="n">
         <v>0</v>
@@ -65779,39 +65779,39 @@
     <row r="1572">
       <c r="A1572" s="8" t="inlineStr">
         <is>
-          <t>#01571</t>
+          <t>#01572</t>
         </is>
       </c>
       <c r="B1572" s="8" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="C1572" s="8" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1572" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1572" s="9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F1572" s="9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G1572" s="9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H1572" s="9" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I1572" s="9" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J1572" s="10" t="n">
-        <v>114772358051</v>
+        <v>117758476365</v>
       </c>
       <c r="K1572" s="8" t="n">
         <v>0</v>
@@ -65820,39 +65820,39 @@
     <row r="1573">
       <c r="A1573" s="8" t="inlineStr">
         <is>
-          <t>#01572</t>
+          <t>#01573</t>
         </is>
       </c>
       <c r="B1573" s="8" t="inlineStr">
         <is>
-          <t>02/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="C1573" s="8" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1573" s="9" t="n">
         <v>8</v>
       </c>
       <c r="E1573" s="9" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="F1573" s="9" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G1573" s="9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H1573" s="9" t="n">
         <v>38</v>
       </c>
       <c r="I1573" s="9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J1573" s="10" t="n">
-        <v>117758476365</v>
+        <v>120375606348</v>
       </c>
       <c r="K1573" s="8" t="n">
         <v>0</v>
@@ -65861,121 +65861,121 @@
     <row r="1574">
       <c r="A1574" s="8" t="inlineStr">
         <is>
-          <t>#01573</t>
+          <t>#01574</t>
         </is>
       </c>
       <c r="B1574" s="8" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>07/08/2026</t>
         </is>
       </c>
       <c r="C1574" s="8" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1574" s="9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1574" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="F1574" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1574" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="H1574" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="I1574" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1574" s="10" t="n">
+        <v>122616604335</v>
+      </c>
+      <c r="K1574" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" s="16" t="inlineStr">
+        <is>
+          <t>#01575</t>
+        </is>
+      </c>
+      <c r="B1575" s="16" t="inlineStr">
+        <is>
+          <t>09/08/2026</t>
+        </is>
+      </c>
+      <c r="C1575" s="16" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+      <c r="D1575" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1575" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F1575" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1575" s="17" t="n">
         <v>27</v>
       </c>
-      <c r="F1574" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="G1574" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="H1574" s="9" t="n">
-        <v>38</v>
-      </c>
-      <c r="I1574" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="J1574" s="10" t="n">
-        <v>120375606348</v>
-      </c>
-      <c r="K1574" s="8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1575">
-      <c r="A1575" s="8" t="inlineStr">
-        <is>
-          <t>#01574</t>
-        </is>
-      </c>
-      <c r="B1575" s="8" t="inlineStr">
-        <is>
-          <t>07/08/2026</t>
-        </is>
-      </c>
-      <c r="C1575" s="8" t="inlineStr">
-        <is>
-          <t>Thứ 6</t>
-        </is>
-      </c>
-      <c r="D1575" s="9" t="n">
-        <v>18</v>
-      </c>
-      <c r="E1575" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="F1575" s="9" t="n">
+      <c r="H1575" s="17" t="n">
         <v>31</v>
       </c>
-      <c r="G1575" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H1575" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="I1575" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="J1575" s="10" t="n">
-        <v>122616604335</v>
-      </c>
-      <c r="K1575" s="8" t="n">
+      <c r="I1575" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="J1575" s="18" t="n">
+        <v>16447584000</v>
+      </c>
+      <c r="K1575" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" s="16" t="inlineStr">
         <is>
-          <t>#01575</t>
+          <t>#01576</t>
         </is>
       </c>
       <c r="B1576" s="16" t="inlineStr">
         <is>
-          <t>09/08/2026</t>
+          <t>12/08/2026</t>
         </is>
       </c>
       <c r="C1576" s="16" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1576" s="17" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E1576" s="17" t="n">
         <v>17</v>
       </c>
       <c r="F1576" s="17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1576" s="17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H1576" s="17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I1576" s="17" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J1576" s="18" t="n">
-        <v>16447584000</v>
+        <v>18210978000</v>
       </c>
       <c r="K1576" s="16" t="n">
         <v>0</v>
@@ -65984,39 +65984,39 @@
     <row r="1577">
       <c r="A1577" s="16" t="inlineStr">
         <is>
-          <t>#01576</t>
+          <t>#01577</t>
         </is>
       </c>
       <c r="B1577" s="16" t="inlineStr">
         <is>
-          <t>12/08/2026</t>
+          <t>14/08/2026</t>
         </is>
       </c>
       <c r="C1577" s="16" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1577" s="17" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1577" s="17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F1577" s="17" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G1577" s="17" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1577" s="17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I1577" s="17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J1577" s="18" t="n">
-        <v>18210978000</v>
+        <v>20050493000</v>
       </c>
       <c r="K1577" s="16" t="n">
         <v>0</v>
@@ -66025,39 +66025,39 @@
     <row r="1578">
       <c r="A1578" s="16" t="inlineStr">
         <is>
-          <t>#01577</t>
+          <t>#01578</t>
         </is>
       </c>
       <c r="B1578" s="16" t="inlineStr">
         <is>
-          <t>14/08/2026</t>
+          <t>16/08/2026</t>
         </is>
       </c>
       <c r="C1578" s="16" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1578" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1578" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E1578" s="17" t="n">
-        <v>9</v>
-      </c>
       <c r="F1578" s="17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G1578" s="17" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H1578" s="17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I1578" s="17" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J1578" s="18" t="n">
-        <v>20050493000</v>
+        <v>22133497500</v>
       </c>
       <c r="K1578" s="16" t="n">
         <v>0</v>
@@ -66066,39 +66066,39 @@
     <row r="1579">
       <c r="A1579" s="16" t="inlineStr">
         <is>
-          <t>#01578</t>
+          <t>#01579</t>
         </is>
       </c>
       <c r="B1579" s="16" t="inlineStr">
         <is>
-          <t>16/08/2026</t>
+          <t>19/08/2026</t>
         </is>
       </c>
       <c r="C1579" s="16" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1579" s="17" t="n">
         <v>6</v>
       </c>
       <c r="E1579" s="17" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F1579" s="17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G1579" s="17" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H1579" s="17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I1579" s="17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1579" s="18" t="n">
-        <v>22133497500</v>
+        <v>24507110500</v>
       </c>
       <c r="K1579" s="16" t="n">
         <v>0</v>
@@ -66107,39 +66107,39 @@
     <row r="1580">
       <c r="A1580" s="16" t="inlineStr">
         <is>
-          <t>#01579</t>
+          <t>#01580</t>
         </is>
       </c>
       <c r="B1580" s="16" t="inlineStr">
         <is>
-          <t>19/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="C1580" s="16" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1580" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1580" s="17" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F1580" s="17" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G1580" s="17" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H1580" s="17" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I1580" s="17" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J1580" s="18" t="n">
-        <v>24507110500</v>
+        <v>26637873000</v>
       </c>
       <c r="K1580" s="16" t="n">
         <v>0</v>
@@ -66148,39 +66148,39 @@
     <row r="1581">
       <c r="A1581" s="16" t="inlineStr">
         <is>
-          <t>#01580</t>
+          <t>#01581</t>
         </is>
       </c>
       <c r="B1581" s="16" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="C1581" s="16" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1581" s="17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E1581" s="17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F1581" s="17" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G1581" s="17" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H1581" s="17" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I1581" s="17" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J1581" s="18" t="n">
-        <v>26637873000</v>
+        <v>28975123500</v>
       </c>
       <c r="K1581" s="16" t="n">
         <v>0</v>
@@ -66189,39 +66189,39 @@
     <row r="1582">
       <c r="A1582" s="16" t="inlineStr">
         <is>
-          <t>#01581</t>
+          <t>#01582</t>
         </is>
       </c>
       <c r="B1582" s="16" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>26/08/2026</t>
         </is>
       </c>
       <c r="C1582" s="16" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1582" s="17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E1582" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1582" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1582" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="F1582" s="17" t="n">
-        <v>17</v>
-      </c>
-      <c r="G1582" s="17" t="n">
-        <v>22</v>
-      </c>
       <c r="H1582" s="17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I1582" s="17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1582" s="18" t="n">
-        <v>28975123500</v>
+        <v>31682191000</v>
       </c>
       <c r="K1582" s="16" t="n">
         <v>0</v>
@@ -66230,39 +66230,39 @@
     <row r="1583">
       <c r="A1583" s="16" t="inlineStr">
         <is>
-          <t>#01582</t>
+          <t>#01583</t>
         </is>
       </c>
       <c r="B1583" s="16" t="inlineStr">
         <is>
-          <t>26/08/2026</t>
+          <t>28/08/2026</t>
         </is>
       </c>
       <c r="C1583" s="16" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1583" s="17" t="n">
         <v>3</v>
       </c>
       <c r="E1583" s="17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F1583" s="17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G1583" s="17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H1583" s="17" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I1583" s="17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J1583" s="18" t="n">
-        <v>31682191000</v>
+        <v>33904731500</v>
       </c>
       <c r="K1583" s="16" t="n">
         <v>0</v>
@@ -66271,39 +66271,39 @@
     <row r="1584">
       <c r="A1584" s="16" t="inlineStr">
         <is>
-          <t>#01583</t>
+          <t>#01584</t>
         </is>
       </c>
       <c r="B1584" s="16" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="C1584" s="16" t="inlineStr">
         <is>
-          <t>Thứ 6</t>
+          <t>Chủ Nhật</t>
         </is>
       </c>
       <c r="D1584" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1584" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E1584" s="17" t="n">
-        <v>13</v>
-      </c>
       <c r="F1584" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1584" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="G1584" s="17" t="n">
-        <v>22</v>
-      </c>
       <c r="H1584" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1584" s="17" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J1584" s="18" t="n">
-        <v>33904731500</v>
+        <v>36644788500</v>
       </c>
       <c r="K1584" s="16" t="n">
         <v>0</v>
@@ -66312,39 +66312,39 @@
     <row r="1585">
       <c r="A1585" s="16" t="inlineStr">
         <is>
-          <t>#01584</t>
+          <t>#01585</t>
         </is>
       </c>
       <c r="B1585" s="16" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="C1585" s="16" t="inlineStr">
         <is>
-          <t>Chủ Nhật</t>
+          <t>Thứ 4</t>
         </is>
       </c>
       <c r="D1585" s="17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E1585" s="17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F1585" s="17" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G1585" s="17" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H1585" s="17" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I1585" s="17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J1585" s="18" t="n">
-        <v>36644788500</v>
+        <v>38804848000</v>
       </c>
       <c r="K1585" s="16" t="n">
         <v>0</v>
@@ -66353,82 +66353,82 @@
     <row r="1586">
       <c r="A1586" s="16" t="inlineStr">
         <is>
-          <t>#01585</t>
+          <t>#01586</t>
         </is>
       </c>
       <c r="B1586" s="16" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="C1586" s="16" t="inlineStr">
         <is>
-          <t>Thứ 4</t>
+          <t>Thứ 6</t>
         </is>
       </c>
       <c r="D1586" s="17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1586" s="17" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F1586" s="17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G1586" s="17" t="n">
         <v>29</v>
       </c>
       <c r="H1586" s="17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I1586" s="17" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1586" s="18" t="n">
-        <v>38804848000</v>
+        <v>43022978000</v>
       </c>
       <c r="K1586" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="1587">
-      <c r="A1587" s="16" t="inlineStr">
-        <is>
-          <t>#01586</t>
-        </is>
-      </c>
-      <c r="B1587" s="16" t="inlineStr">
-        <is>
-          <t>04/09/2026</t>
-        </is>
-      </c>
-      <c r="C1587" s="16" t="inlineStr">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>#01564</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>18/09/2026</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
         <is>
           <t>Thứ 6</t>
         </is>
       </c>
-      <c r="D1587" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="E1587" s="17" t="n">
-        <v>21</v>
-      </c>
-      <c r="F1587" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="G1587" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="H1587" s="17" t="n">
-        <v>34</v>
-      </c>
-      <c r="I1587" s="17" t="n">
-        <v>45</v>
-      </c>
-      <c r="J1587" s="18" t="n">
-        <v>43022978000</v>
-      </c>
-      <c r="K1587" s="16" t="n">
+      <c r="D1587" t="n">
+        <v>7</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>12</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1587" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1587" t="n">
+        <v>41</v>
+      </c>
+      <c r="I1587" t="n">
+        <v>43</v>
+      </c>
+      <c r="J1587" t="n">
+        <v>86148921500</v>
+      </c>
+      <c r="K1587" t="n">
         <v>0</v>
       </c>
     </row>
@@ -66444,7 +66444,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="20" min="1" max="1"/>
     <col width="61" customWidth="1" style="20" min="2" max="2"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -64632,7 +64632,7 @@
         <v>38</v>
       </c>
       <c r="J1566" t="n">
-        <v>0</v>
+        <v>96163598000</v>
       </c>
       <c r="K1566" t="n">
         <v>0</v>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -15,16 +15,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_([$VND]\ * #,##0_);_([$VND]\ * \(#,##0\);_([$VND]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="00"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +46,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,13 +54,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1566"/>
+  <dimension ref="A1:K1567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64644,6 +64678,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>#01566</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>23/09/2026</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D1567" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1567" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1567" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1567" t="n">
+        <v>15</v>
+      </c>
+      <c r="H1567" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1567" t="n">
+        <v>26</v>
+      </c>
+      <c r="J1567" t="n">
+        <v>110492809000</v>
+      </c>
+      <c r="K1567" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -15,16 +15,28 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_([$VND]\ * #,##0_);_([$VND]\ * \(#,##0\);_([$VND]\ * &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="00"/>
+    <numFmt numFmtId="166" formatCode="#,##0 &quot;VND&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,13 +55,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -415,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1567"/>
+  <dimension ref="A1:K1568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64685,6 +64720,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>#01567</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="D1568" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1568" t="n">
+        <v>15</v>
+      </c>
+      <c r="F1568" t="n">
+        <v>18</v>
+      </c>
+      <c r="G1568" t="n">
+        <v>28</v>
+      </c>
+      <c r="H1568" t="n">
+        <v>33</v>
+      </c>
+      <c r="I1568" t="n">
+        <v>36</v>
+      </c>
+      <c r="J1568" t="n">
+        <v>124270821500</v>
+      </c>
+      <c r="K1568" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1568"/>
+  <dimension ref="A1:K1569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64761,6 +64761,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>#01568</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+      <c r="D1569" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1569" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1569" t="n">
+        <v>13</v>
+      </c>
+      <c r="G1569" t="n">
+        <v>25</v>
+      </c>
+      <c r="H1569" t="n">
+        <v>31</v>
+      </c>
+      <c r="I1569" t="n">
+        <v>39</v>
+      </c>
+      <c r="J1569" t="n">
+        <v>139776125000</v>
+      </c>
+      <c r="K1569" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1569"/>
+  <dimension ref="A1:K1570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64802,6 +64802,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>#01569</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D1570" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1570" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1570" t="n">
+        <v>24</v>
+      </c>
+      <c r="G1570" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1570" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1570" t="n">
+        <v>33</v>
+      </c>
+      <c r="J1570" t="n">
+        <v>158758806000</v>
+      </c>
+      <c r="K1570" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1570"/>
+  <dimension ref="A1:K1571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64843,6 +64843,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>#01570</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>02/10/2026</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="D1571" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1571" t="n">
+        <v>6</v>
+      </c>
+      <c r="F1571" t="n">
+        <v>20</v>
+      </c>
+      <c r="G1571" t="n">
+        <v>27</v>
+      </c>
+      <c r="H1571" t="n">
+        <v>31</v>
+      </c>
+      <c r="I1571" t="n">
+        <v>41</v>
+      </c>
+      <c r="J1571" t="n">
+        <v>178900548500</v>
+      </c>
+      <c r="K1571" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="165" formatCode="00"/>
     <numFmt numFmtId="166" formatCode="#,##0 &quot;VND&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,13 +38,25 @@
       <color rgb="001E3A8A"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -73,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -84,6 +96,9 @@
     </xf>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1571"/>
+  <dimension ref="A1:K1572"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64884,6 +64899,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>#01571</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+      <c r="D1572" t="n">
+        <v>15</v>
+      </c>
+      <c r="E1572" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1572" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1572" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1572" t="n">
+        <v>40</v>
+      </c>
+      <c r="I1572" t="n">
+        <v>45</v>
+      </c>
+      <c r="J1572" t="n">
+        <v>199576277000</v>
+      </c>
+      <c r="K1572" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1572"/>
+  <dimension ref="A1:K1573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64940,6 +64940,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>#01572</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D1573" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1573" t="n">
+        <v>14</v>
+      </c>
+      <c r="F1573" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1573" t="n">
+        <v>37</v>
+      </c>
+      <c r="H1573" t="n">
+        <v>41</v>
+      </c>
+      <c r="I1573" t="n">
+        <v>43</v>
+      </c>
+      <c r="J1573" t="n">
+        <v>14163913000</v>
+      </c>
+      <c r="K1573" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1573"/>
+  <dimension ref="A1:K1574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -64981,6 +64981,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>#01573</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="D1574" t="n">
+        <v>5</v>
+      </c>
+      <c r="E1574" t="n">
+        <v>7</v>
+      </c>
+      <c r="F1574" t="n">
+        <v>12</v>
+      </c>
+      <c r="G1574" t="n">
+        <v>23</v>
+      </c>
+      <c r="H1574" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1574" t="n">
+        <v>41</v>
+      </c>
+      <c r="J1574" t="n">
+        <v>15889161000</v>
+      </c>
+      <c r="K1574" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1574"/>
+  <dimension ref="A1:K1575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65022,6 +65022,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>#01574</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>11/10/2026</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+      <c r="D1575" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1575" t="n">
+        <v>9</v>
+      </c>
+      <c r="F1575" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1575" t="n">
+        <v>29</v>
+      </c>
+      <c r="H1575" t="n">
+        <v>30</v>
+      </c>
+      <c r="I1575" t="n">
+        <v>44</v>
+      </c>
+      <c r="J1575" t="n">
+        <v>17917606500</v>
+      </c>
+      <c r="K1575" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1575"/>
+  <dimension ref="A1:K1576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65063,6 +65063,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>#01575</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D1576" t="n">
+        <v>6</v>
+      </c>
+      <c r="E1576" t="n">
+        <v>16</v>
+      </c>
+      <c r="F1576" t="n">
+        <v>19</v>
+      </c>
+      <c r="G1576" t="n">
+        <v>21</v>
+      </c>
+      <c r="H1576" t="n">
+        <v>34</v>
+      </c>
+      <c r="I1576" t="n">
+        <v>43</v>
+      </c>
+      <c r="J1576" t="n">
+        <v>20329744500</v>
+      </c>
+      <c r="K1576" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1576"/>
+  <dimension ref="A1:K1577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65104,6 +65104,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>#01576</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="D1577" t="n">
+        <v>9</v>
+      </c>
+      <c r="E1577" t="n">
+        <v>20</v>
+      </c>
+      <c r="F1577" t="n">
+        <v>26</v>
+      </c>
+      <c r="G1577" t="n">
+        <v>35</v>
+      </c>
+      <c r="H1577" t="n">
+        <v>36</v>
+      </c>
+      <c r="I1577" t="n">
+        <v>38</v>
+      </c>
+      <c r="J1577" t="n">
+        <v>22839868000</v>
+      </c>
+      <c r="K1577" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1577"/>
+  <dimension ref="A1:K1578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65145,6 +65145,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>#01577</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Chủ Nhật</t>
+        </is>
+      </c>
+      <c r="D1578" t="n">
+        <v>10</v>
+      </c>
+      <c r="E1578" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1578" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1578" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1578" t="n">
+        <v>40</v>
+      </c>
+      <c r="I1578" t="n">
+        <v>44</v>
+      </c>
+      <c r="J1578" t="n">
+        <v>26444954000</v>
+      </c>
+      <c r="K1578" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1578"/>
+  <dimension ref="A1:K1579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65186,6 +65186,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>#01578</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>Thứ 4</t>
+        </is>
+      </c>
+      <c r="D1579" t="n">
+        <v>4</v>
+      </c>
+      <c r="E1579" t="n">
+        <v>10</v>
+      </c>
+      <c r="F1579" t="n">
+        <v>14</v>
+      </c>
+      <c r="G1579" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1579" t="n">
+        <v>25</v>
+      </c>
+      <c r="I1579" t="n">
+        <v>44</v>
+      </c>
+      <c r="J1579" t="n">
+        <v>31281381500</v>
+      </c>
+      <c r="K1579" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>

--- a/Vietlott_Mega_645_Full_Results.xlsx
+++ b/Vietlott_Mega_645_Full_Results.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1579"/>
+  <dimension ref="A1:K1580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="10.19921875" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -65227,6 +65227,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>#01579</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Thứ 6</t>
+        </is>
+      </c>
+      <c r="D1580" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1580" t="n">
+        <v>5</v>
+      </c>
+      <c r="F1580" t="n">
+        <v>11</v>
+      </c>
+      <c r="G1580" t="n">
+        <v>22</v>
+      </c>
+      <c r="H1580" t="n">
+        <v>32</v>
+      </c>
+      <c r="I1580" t="n">
+        <v>40</v>
+      </c>
+      <c r="J1580" t="n">
+        <v>13983147000</v>
+      </c>
+      <c r="K1580" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
